--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -1,43 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,26 +55,105 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -330,10 +419,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_ratings</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>test_ratio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_recommendations</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>m (percentile)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hit Rate @10</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precision @10</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recall @10</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>80th pct</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Greedy baseline. Recommends same top-10 popular anime to all users. No personalisation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -29,7 +29,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,12 +78,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -424,10 +432,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -520,6 +528,286 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, cosine similarity weighted by user rating. Rare genres weighted higher than common ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Collaborative AE. Dense 128→32→128, Sigmoid output, masked MSE loss. Adam, epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -432,10 +432,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -808,6 +808,41 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam, epochs=20, batch=256, patience=3.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,14 +82,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -176,44 +169,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -240,15 +233,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -275,7 +267,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -287,142 +278,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -432,12 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -502,8 +517,10 @@
       <c r="B2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0.3</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>10</v>
@@ -514,13 +531,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4468</v>
+        <v>0.032</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.032</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -529,321 +546,191 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>BoW + Cosine Similarity</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>BoW + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+      <c r="F4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, cosine similarity weighted by user rating. Rare genres weighted higher than common ones.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BoW + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+      <c r="F5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>BoW + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
+      <c r="F6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative AE. Dense 128→32→128, Sigmoid output, masked MSE loss. Adam, epochs=20, batch=128, patience=3, train_users=10000.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>BoW + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TF-IDF + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Content-based. TF-IDF genre vectors, cosine similarity weighted by user rating. Rare genres weighted higher than common ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SVD Collaborative Filtering</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.3515</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0.1852</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Autoencoder</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Collaborative AE. Dense 128→32→128, Sigmoid output, masked MSE loss. Adam, epochs=20, batch=128, patience=3, train_users=10000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>NCF (Neural Collaborative Filtering)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam, epochs=20, batch=256, patience=3.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Runs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +69,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,286 +439,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Run #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>min_ratings</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>test_ratio</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_recommendations</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>m (percentile)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>epochs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>batch_size</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>patience</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>embed_dim</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_components</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>train_users</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate @10</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Precision @10</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Recall @10</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Baseline (Popularity)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>80th pct</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Greedy baseline. Recommends same top-10 popular anime to all users. No personalisation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>BoW + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Content-based. Genre BoW vectors, cosine similarity weighted by user rating. No collaborative signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TF-IDF + Cosine Similarity</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Content-based. TF-IDF genre vectors, cosine similarity weighted by user rating. Rare genres weighted higher than common ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SVD Collaborative Filtering</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Autoencoder</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Collaborative AE. Dense 128→32→128, Sigmoid output, masked MSE loss. Adam, epochs=20, batch=128, patience=3, train_users=10000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>NCF (Neural Collaborative Filtering)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>leave-one-out</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam, epochs=20, batch=256, patience=3.</t>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>What changed / Comment</t>
         </is>
       </c>
     </row>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,9 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,25 +447,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -539,6 +547,686 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>What changed / Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:31</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:31</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:31</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:31</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:31</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:42</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:01</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:13</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:13</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:14</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
       </c>
     </row>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,7 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1230,6 +1231,803 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:33</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:33</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:33</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:33</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:34</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:44</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>602.5</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:47</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:47</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:47</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:47</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:48</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SVD n_components=50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -456,17 +456,19 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -502,50 +504,60 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>m_percentile</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>epochs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>patience</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>embed_dim</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>n_components</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>train_users</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Train time (s)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate @10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Precision @10</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Recall @10</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>What changed / Comment</t>
         </is>
@@ -576,10 +588,8 @@
       <c r="F2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,16 +616,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0.0032</v>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O2" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
         </is>
@@ -676,16 +696,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.0015</v>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O3" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -746,16 +776,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.002</v>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O4" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
@@ -806,24 +846,34 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0.0298</v>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O5" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
@@ -854,38 +904,48 @@
       <c r="F6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0.0014</v>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O6" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
         </is>
@@ -916,38 +976,48 @@
       <c r="F7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0.001</v>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
         </is>
@@ -1008,16 +1078,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0.0015</v>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -1078,16 +1158,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0.0015</v>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -1148,16 +1238,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.002</v>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O10" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
@@ -1208,24 +1308,34 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0.0298</v>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O11" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
@@ -1256,10 +1366,8 @@
       <c r="F12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1291,20 +1399,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>0.0032</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
         </is>
       </c>
+      <c r="S12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1366,20 +1480,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>0.0015</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
       </c>
+      <c r="S13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1441,20 +1561,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>0.002</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
       </c>
+      <c r="S14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1501,31 +1627,37 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
         <v>12.6</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>0.0298</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
       </c>
+      <c r="S15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1552,45 +1684,51 @@
       <c r="F16" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>12.2</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>0.0014</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
         </is>
       </c>
+      <c r="S16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1617,45 +1755,51 @@
       <c r="F17" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
         <v>602.5</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
         </is>
       </c>
+      <c r="S17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1682,10 +1826,8 @@
       <c r="F18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G18" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1717,20 +1859,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>0.0032</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
       </c>
+      <c r="S18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1757,10 +1905,8 @@
       <c r="F19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G19" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1792,20 +1938,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>0.0032</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
       </c>
+      <c r="S19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1867,20 +2019,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>0.0015</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>BoW cosine run</t>
         </is>
       </c>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1942,20 +2100,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>0.002</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>TF-IDF cosine run</t>
         </is>
       </c>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2002,29 +2166,662 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
         <v>11.1</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>0.0298</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>SVD n_components=50</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:49</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run 50th percentil</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:49</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run 50th percentil</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:50</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:13</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run 90th percentile</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:17</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:30</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:37</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:38</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
         </is>
       </c>
     </row>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -457,18 +457,20 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -509,55 +511,65 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>min_rating_threshold</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sublinear_tf</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>epochs</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>patience</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>embed_dim</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>n_components</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>train_users</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Train time (s)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate @10</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision @10</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Recall @10</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>What changed / Comment</t>
         </is>
@@ -626,16 +638,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.0032</v>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
         </is>
@@ -671,10 +693,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -706,16 +726,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0.0015</v>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -751,14 +781,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -786,16 +814,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.002</v>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
@@ -851,29 +889,39 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0.0298</v>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
@@ -909,43 +957,53 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0.0014</v>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
         </is>
@@ -981,43 +1039,53 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0.001</v>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
         </is>
@@ -1053,10 +1121,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1088,16 +1154,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0.0015</v>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -1133,10 +1209,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1168,16 +1242,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.0015</v>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
@@ -1213,14 +1297,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1248,16 +1330,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0.002</v>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
@@ -1313,29 +1405,39 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0.0298</v>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
@@ -1404,21 +1506,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0.0032</v>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q12" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
         </is>
       </c>
-      <c r="S12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1450,10 +1562,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1485,21 +1595,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>0.0015</v>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating.</t>
         </is>
       </c>
-      <c r="S13" s="2" t="n"/>
+      <c r="U13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1531,14 +1651,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1566,21 +1684,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0.002</v>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q14" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>Content-based. TF-IDF genre vectors, L2-normalised. Rare genres weighted higher than common ones.</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1632,32 +1760,42 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>12.6</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>0.0298</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
         </is>
       </c>
-      <c r="S15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1689,46 +1827,56 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>12.2</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0.0014</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Dense 128→32→128, Sigmoid, masked MSE. epochs=20, batch=128, patience=3, train_users=10000.</t>
         </is>
       </c>
-      <c r="S16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1760,46 +1908,56 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
         <v>602.5</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>0.001</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>User+anime embeddings (32d), concat→Dense64→Dense32→1. MSE loss, Adam. epochs=20, batch=256, patience=3.</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1864,21 +2022,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>0.0032</v>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1943,21 +2111,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>0.0032</v>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
       </c>
-      <c r="S19" s="2" t="n"/>
+      <c r="U19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1989,10 +2167,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -2024,21 +2200,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>0.0015</v>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q20" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>BoW cosine run</t>
         </is>
       </c>
-      <c r="S20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2070,14 +2256,12 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2105,21 +2289,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>0.002</v>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q21" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>TF-IDF cosine run</t>
         </is>
       </c>
-      <c r="S21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2171,32 +2365,42 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
         <v>11.1</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>0.0298</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>SVD n_components=50</t>
         </is>
       </c>
-      <c r="S22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2261,21 +2465,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>0.0014</v>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q23" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run 50th percentil</t>
         </is>
       </c>
-      <c r="S23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2340,21 +2554,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>0.0016</v>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q24" s="2" t="n">
         <v>0.016</v>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run 50th percentil</t>
         </is>
       </c>
-      <c r="S24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2419,21 +2643,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0.0016</v>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0.016</v>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
       </c>
-      <c r="S25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2498,16 +2732,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>0.0054</v>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q26" s="2" t="n">
         <v>0.054</v>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run 90th percentile</t>
         </is>
@@ -2576,16 +2820,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0.0032</v>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q27" s="2" t="n">
         <v>0.032</v>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
@@ -2654,16 +2908,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>0.0054</v>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q28" s="2" t="n">
         <v>0.054</v>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
@@ -2732,16 +2996,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>0.0069</v>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q29" s="2" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
         </is>
@@ -2810,18 +3084,3324 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>0.0076</v>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q30" s="2" t="n">
         <v>0.076</v>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:23</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:25</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:26</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:30</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:31</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:32</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:33</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:34</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:35</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:35</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:37</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:38</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:45</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:49</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:52</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:54</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:54</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:54</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:55</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:55</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:55</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:55</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:55</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:56</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:59</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:59</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:59</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:59</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:00</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:00</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:01</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I61" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:01</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:01</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:03</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:04</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:04</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:05</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>Baseline popularity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:06</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>BoW cosine run</t>
         </is>
       </c>
     </row>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6405,6 +6405,660 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:20</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF cosine run</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:21</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>SVD run</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:24</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:29</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:32</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:34</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:35</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:36</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7059,6 +7059,566 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:54</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:55</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:05</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:05</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:11</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>265.7</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:55</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>2427.4</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>NCF run</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 20:28</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>1011.4</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>NCF run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,8 @@
     <col width="17" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -574,6 +575,16 @@
           <t>What changed / Comment</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pairs_per_user</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>n_per_user</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -7617,6 +7628,748 @@
         <is>
           <t>NCF run</t>
         </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:49</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S84" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:49</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S85" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:49</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S86" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:50</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S87" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:53</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="S88" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>[v2] Dense 128→32→128, Sigmoid, BPR ranking loss. epochs=20, batch=128, patience=3, pairs_per_user=20, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:54</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="S89" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>[v2] User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:57</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="S90" s="2" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 run</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:00</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="S91" s="2" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 run</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:W129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="40" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -585,6 +586,11 @@
           <t>n_per_user</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -8096,7 +8102,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>[v2] Dense 128→32→128, Sigmoid, BPR ranking loss. epochs=20, batch=128, patience=3, pairs_per_user=20, train_users=10000.</t>
+          <t>AE v2 — FIRST v2 RUN. Changes from v1: (1) loss: masked MSE → BPR ranking loss with negative sampling; (2) training: DataLoader over (user,anime,rating) triples → BPR (user,pos,neg) pairs; (3) new param pairs_per_user controls pair density per epoch. Result: marginal HR improvement (0.013→0.024); BPR later replaced in v3.</t>
         </is>
       </c>
       <c r="U88" s="2" t="n">
@@ -8184,7 +8190,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>[v2] User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+          <t>NCF v2 — FIRST v2 RUN. Changes from v1: (1) loss: MSE rating regression → BPR ranking loss (BCEWithLogitsLoss on pos-neg score diff); (2) training: DataLoader over explicit ratings → BPR (user,pos,neg) triples; (3) new param n_per_user controls pairs sampled per user per epoch; (4) negative sampling: rejection-loop (later vectorised in v2 optimisation). Result: HR 0.010→0.109 — correct objective directly optimises ranking.</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -8370,6 +8376,3540 @@
       </c>
       <c r="V91" s="2" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:15</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="S92" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 run</t>
+        </is>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:25</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="S93" s="2" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v2 run</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 04:10</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>1701.1</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="S94" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v2 run</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:09</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S95" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:09</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S96" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:09</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S97" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:09</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S98" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:10</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="S99" s="2" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>AE v3 — FIRST v3 RUN. Changes from v2: (1) loss: BPR (wrong for dense AE) → weighted MSE with confidence weight alpha; (2) user-item matrix: raw normalised [0,1] → mean-centred per user (observed cells - user mean, zeros stay 0, scaled to [-0.5,0.5]); (3) observed mask: precomputed from raw values before centering (fixes target&gt;0 being wrong after centering); (4) patience default: 3→5. Result: HR 0.024→0.201 — correct dense loss + mean-centering removes zero-cell bias.</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:11</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="S100" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:30</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S101" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:30</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S102" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:30</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S103" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:31</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S104" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:32</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S105" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=5, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:33</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S106" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:55</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S107" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 run</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:57</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S108" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:57</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S109" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:57</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S110" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:57</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S111" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 07:58</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S112" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:00</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S113" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:13</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S114" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:18</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S115" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:18</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S116" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:18</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S117" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:19</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S118" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:19</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S119" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:21</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S120" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:29</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="S121" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:30</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="S122" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, explicit obs mask. epochs=20, batch=128, patience=3, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:40</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S123" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, target&gt;0 mask (above-avg items only, correct for top-N ranking). epochs=200, batch=128, patience=10, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:57</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S124" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:57</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S125" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:57</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S126" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 08:58</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S127" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:00</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S128" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, target&gt;0 mask (above-avg items only, correct for top-N ranking). epochs=200, batch=128, patience=10, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:01</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S129" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/report/model_performance_tracker.xlsx
+++ b/report/model_performance_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W129"/>
+  <dimension ref="A1:W135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11912,6 +11912,572 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:49</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (Popularity)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S130" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian popularity baseline. m=80th pct. Recommends same top-10 to all users, no personalisation.</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:49</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>BoW + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S131" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. Genre BoW, L2-normalised, dot-product cosine. Weighted by user rating. min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:49</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF + Cosine Similarity</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S132" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>Content-based. TF-IDF genre vectors, L2-normalised. sublinear_tf=False, min_rating_threshold=1.</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:50</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>SVD Collaborative Filtering</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="S133" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>Collaborative filtering. TruncatedSVD n_components=50. Factorises user-item rating matrix.</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:52</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S134" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>Autoencoder v3 — weighted MSE (alpha=5.0), mean-centred rows, target&gt;0 mask (above-avg items only, correct for top-N ranking). epochs=200, batch=128, patience=10, train_users=10000.</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:54</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>NCF (Neural Collaborative Filtering)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>leave-one-out</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S135" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>NCF v2 — User+anime embeddings (32d), concat→Dense64→Dense32→1. BPR ranking loss, Adam. epochs=20, batch=256, patience=3, n_per_user=10.</t>
+        </is>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
